--- a/slides/장학사_엑셀/실습데이터/예제2_방과후학교_2줄머리글/정답키.xlsx
+++ b/slides/장학사_엑셀/실습데이터/예제2_방과후학교_2줄머리글/정답키.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>영어회화</t>
+          <t>독서논술</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -526,10 +526,10 @@
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -545,7 +545,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>영어회화</t>
+          <t>독서논술</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -573,7 +573,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>수학사고력</t>
+          <t>한자교실</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -585,7 +585,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -601,7 +601,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>수학사고력</t>
+          <t>한자교실</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -613,7 +613,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -624,12 +624,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>예체능</t>
+          <t>교과</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>코딩</t>
+          <t>영문법</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -641,7 +641,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -652,12 +652,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>예체능</t>
+          <t>교과</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>코딩</t>
+          <t>영문법</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -669,7 +669,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -680,12 +680,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>예체능</t>
+          <t>교과</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>바이올린</t>
+          <t>과학실험</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -697,7 +697,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -708,12 +708,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>예체능</t>
+          <t>교과</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>바이올린</t>
+          <t>과학실험</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -727,17 +727,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>나래초</t>
+          <t>가람초</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>교과</t>
+          <t>예체능</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>영어회화</t>
+          <t>바이올린</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -746,26 +746,26 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>나래초</t>
+          <t>가람초</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>교과</t>
+          <t>예체능</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>영어회화</t>
+          <t>바이올린</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -774,26 +774,26 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>나래초</t>
+          <t>가람초</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>교과</t>
+          <t>예체능</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>독서논술</t>
+          <t>난타</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -802,26 +802,26 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>나래초</t>
+          <t>가람초</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>교과</t>
+          <t>예체능</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>독서논술</t>
+          <t>난타</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -830,16 +830,16 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>나래초</t>
+          <t>가람초</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>방송댄스</t>
+          <t>농구교실</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -861,13 +861,13 @@
         <v>1</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>나래초</t>
+          <t>가람초</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>방송댄스</t>
+          <t>농구교실</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -889,13 +889,13 @@
         <v>1</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>나래초</t>
+          <t>가람초</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>축구교실</t>
+          <t>미술교실</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -923,7 +923,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>나래초</t>
+          <t>가람초</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>축구교실</t>
+          <t>미술교실</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -945,23 +945,23 @@
         <v>2</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>다온초</t>
+          <t>가람초</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>교과</t>
+          <t>정보</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>한국사</t>
+          <t>3D프린팅</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -973,23 +973,23 @@
         <v>1</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>다온초</t>
+          <t>가람초</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>교과</t>
+          <t>정보</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>한국사</t>
+          <t>3D프린팅</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1001,23 +1001,23 @@
         <v>1</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>다온초</t>
+          <t>가람초</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>교과</t>
+          <t>정보</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>영어회화</t>
+          <t>드론교실</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1029,23 +1029,23 @@
         <v>2</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>다온초</t>
+          <t>가람초</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>교과</t>
+          <t>정보</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>영어회화</t>
+          <t>드론교실</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1054,26 +1054,26 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>다온초</t>
+          <t>나래초</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>예체능</t>
+          <t>교과</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>코딩</t>
+          <t>과학실험</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1082,26 +1082,26 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>다온초</t>
+          <t>나래초</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>예체능</t>
+          <t>교과</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>코딩</t>
+          <t>과학실험</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1110,26 +1110,26 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>다온초</t>
+          <t>나래초</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>예체능</t>
+          <t>교과</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>바이올린</t>
+          <t>영어회화</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1138,26 +1138,26 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>다온초</t>
+          <t>나래초</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>예체능</t>
+          <t>교과</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>바이올린</t>
+          <t>영어회화</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1166,26 +1166,26 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>11</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>다온초</t>
+          <t>나래초</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>예체능</t>
+          <t>교과</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>미술</t>
+          <t>한자교실</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1194,35 +1194,5055 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>나래초</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>한자교실</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>나래초</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>한국사</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>나래초</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>한국사</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>나래초</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>피아노</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>나래초</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>피아노</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>나래초</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>바이올린</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>나래초</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>바이올린</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>나래초</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>방송댄스</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>나래초</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>방송댄스</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>나래초</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>미술교실</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>나래초</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>미술교실</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>나래초</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>로봇과학</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>나래초</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>로봇과학</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
           <t>다온초</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>예체능</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>미술</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>과학실험</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>다온초</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>과학실험</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>다온초</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>시사토론</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>다온초</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>시사토론</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>다온초</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>영문법</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>다온초</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>영문법</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>다온초</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>수학사고력</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>다온초</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>수학사고력</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>다온초</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>농구교실</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>다온초</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>농구교실</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>다온초</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>배드민턴</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>다온초</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>배드민턴</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>다온초</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>축구교실</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>다온초</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>축구교실</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>다온초</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>태권도</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>다온초</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>태권도</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>다온초</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>피아노</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>다온초</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>피아노</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>다온초</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>드론교실</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>다온초</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>드론교실</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>글쓰기교실</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>글쓰기교실</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>한국사</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>한국사</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>사회탐구</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>사회탐구</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>수학사고력</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>수학사고력</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>시사토론</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>시사토론</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>미술교실</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>미술교실</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>합창단</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>합창단</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>방송댄스</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>방송댄스</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>바이올린</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>바이올린</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>태권도</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>태권도</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>메이커교실</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>메이커교실</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>과학실험</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>과학실험</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>한국사</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>한국사</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n"/>
+      <c r="F85" s="5" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>독서논술</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>독서논술</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>영어회화</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>영어회화</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>사회탐구</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>사회탐구</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>합창단</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>합창단</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>농구교실</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>농구교실</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>배드민턴</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>배드민턴</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>미술교실</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>미술교실</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>AI기초</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>AI기초</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>3D프린팅</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>3D프린팅</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>시사토론</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>시사토론</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>글쓰기교실</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>글쓰기교실</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>영어회화</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>영어회화</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>과학실험</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>과학실험</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>사회탐구</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>사회탐구</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>바이올린</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>바이올린</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>방송댄스</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>방송댄스</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>난타</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>난타</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>태권도</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>태권도</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>축구교실</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>축구교실</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>드론교실</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>드론교실</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>코딩</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>코딩</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="n"/>
+      <c r="F127" s="5" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>사랑초</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>수학사고력</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>사랑초</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>수학사고력</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>사랑초</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>글쓰기교실</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>사랑초</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>글쓰기교실</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" s="4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>사랑초</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>시사토론</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>사랑초</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>시사토론</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>사랑초</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>영어회화</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" s="4" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>사랑초</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>영어회화</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="n"/>
+      <c r="F135" s="5" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>사랑초</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>방송댄스</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F136" s="4" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>사랑초</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>방송댄스</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F137" s="4" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>사랑초</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>농구교실</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F138" s="4" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>사랑초</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>농구교실</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" s="4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>사랑초</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>피아노</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F140" s="4" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>사랑초</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>피아노</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F141" s="4" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>사랑초</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>축구교실</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" s="4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>사랑초</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>축구교실</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" s="4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>사랑초</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>코딩</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F144" s="4" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>사랑초</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>코딩</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F145" s="4" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>과학실험</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F146" s="4" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>과학실험</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F147" s="4" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>독서논술</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" s="4" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>독서논술</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>사회탐구</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F150" s="4" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>사회탐구</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>수학사고력</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F152" s="4" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>수학사고력</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" s="4" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>한자교실</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>한자교실</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F155" s="4" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>배드민턴</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>배드민턴</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F157" s="4" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>바이올린</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" s="4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>바이올린</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>난타</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>난타</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F161" s="4" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>미술교실</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F162" s="4" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>미술교실</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>3D프린팅</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F164" s="4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>3D프린팅</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F165" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>AI기초</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F166" s="4" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>AI기초</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F167" s="4" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>한국사</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F168" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>한국사</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F169" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>수학사고력</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" s="4" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>수학사고력</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>독서논술</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F172" s="4" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>독서논술</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F173" s="4" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>사회탐구</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" s="4" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>사회탐구</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F175" s="4" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>바이올린</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F176" s="4" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>바이올린</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F177" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>태권도</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F178" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>태권도</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F179" s="4" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>방송댄스</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" s="4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>방송댄스</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F181" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>피아노</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>피아노</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" s="4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>난타</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F184" s="4" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>난타</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="n"/>
+      <c r="F185" s="5" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>AI기초</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F186" s="4" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>AI기초</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E187" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F187" s="4" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>한자교실</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F188" s="4" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>한자교실</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E189" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F189" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>과학실험</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F190" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>과학실험</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E191" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F191" s="4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>사회탐구</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F192" s="4" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>사회탐구</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E193" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F193" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>독서논술</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E194" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>교과</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>독서논술</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E195" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" s="4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>배드민턴</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E196" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>배드민턴</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>농구교실</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E198" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>농구교실</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E199" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" s="4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>축구교실</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E200" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F200" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>축구교실</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E201" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F201" s="4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>피아노</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E202" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F202" s="4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>예체능</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>피아노</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E203" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F203" s="4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>메이커교실</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E204" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F204" s="4" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>메이커교실</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E205" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F205" s="4" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>3D프린팅</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="E206" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F206" s="4" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>3D프린팅</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="E207" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F207" s="4" t="n">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1235,7 +6255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1279,16 +6299,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>85</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3">
@@ -1298,16 +6318,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>104</v>
+        <v>220</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>109</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4">
@@ -1317,35 +6337,168 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>115</v>
+        <v>239</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>100</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>라온초</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>248</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>마루초</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>바롬초</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>284</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>사랑초</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>아람초</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>311</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>한솔초</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>246</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>해솔초</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>202</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>309</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>294</v>
+      <c r="B12" s="7" t="n">
+        <v>158</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>2481</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>164</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>2751</v>
       </c>
     </row>
   </sheetData>

--- a/slides/장학사_엑셀/실습데이터/예제2_방과후학교_2줄머리글/정답키.xlsx
+++ b/slides/장학사_엑셀/실습데이터/예제2_방과후학교_2줄머리글/정답키.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="데이터형" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="피벗요약" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="설명" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="데이터형" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="피벗요약" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설명" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,15 +461,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F207"/>
+  <dimension ref="A1:H207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,25 +482,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>지역</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>설립</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>영역</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>강좌명</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>학기</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>강좌수</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>수강인원</t>
         </is>
@@ -510,25 +522,35 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>독서논술</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4" t="n">
         <v>18</v>
       </c>
     </row>
@@ -538,25 +560,35 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>독서논술</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -566,25 +598,35 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>한자교실</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -594,25 +636,35 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>한자교실</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="n">
         <v>21</v>
       </c>
     </row>
@@ -622,25 +674,35 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>영문법</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="n">
         <v>16</v>
       </c>
     </row>
@@ -650,25 +712,35 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>영문법</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>36</v>
       </c>
     </row>
@@ -678,25 +750,35 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>과학실험</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -706,23 +788,33 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>과학실험</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -730,25 +822,35 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>바이올린</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="n">
         <v>18</v>
       </c>
     </row>
@@ -758,25 +860,35 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>바이올린</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="n">
         <v>14</v>
       </c>
     </row>
@@ -786,25 +898,35 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>난타</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>29</v>
       </c>
     </row>
@@ -814,25 +936,35 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>난타</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>48</v>
       </c>
     </row>
@@ -842,25 +974,35 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>농구교실</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -870,25 +1012,35 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>농구교실</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -898,25 +1050,35 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>미술교실</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n">
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>28</v>
       </c>
     </row>
@@ -926,25 +1088,35 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>미술교실</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n">
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>23</v>
       </c>
     </row>
@@ -954,25 +1126,35 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>3D프린팅</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -982,25 +1164,35 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>3D프린팅</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="4" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1010,25 +1202,35 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>드론교실</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n">
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>27</v>
       </c>
     </row>
@@ -1038,25 +1240,35 @@
           <t>가람초</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>드론교실</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n">
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>57</v>
       </c>
     </row>
@@ -1066,25 +1278,35 @@
           <t>나래초</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>과학실험</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1094,25 +1316,35 @@
           <t>나래초</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>과학실험</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1122,25 +1354,35 @@
           <t>나래초</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>영어회화</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="n">
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1150,25 +1392,35 @@
           <t>나래초</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>영어회화</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="n">
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>76</v>
       </c>
     </row>
@@ -1178,25 +1430,35 @@
           <t>나래초</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>한자교실</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="n">
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>35</v>
       </c>
     </row>
@@ -1206,25 +1468,35 @@
           <t>나래초</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>한자교실</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="n">
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>54</v>
       </c>
     </row>
@@ -1234,25 +1506,35 @@
           <t>나래초</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>한국사</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="n">
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>28</v>
       </c>
     </row>
@@ -1262,25 +1544,35 @@
           <t>나래초</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>한국사</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n">
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>53</v>
       </c>
     </row>
@@ -1290,25 +1582,35 @@
           <t>나래초</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>피아노</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n">
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>40</v>
       </c>
     </row>
@@ -1318,25 +1620,35 @@
           <t>나래초</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>피아노</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n">
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>46</v>
       </c>
     </row>
@@ -1346,25 +1658,35 @@
           <t>나래초</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>바이올린</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1374,25 +1696,35 @@
           <t>나래초</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>바이올린</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1402,25 +1734,35 @@
           <t>나래초</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>방송댄스</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="4" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1430,25 +1772,35 @@
           <t>나래초</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>방송댄스</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="4" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1458,25 +1810,35 @@
           <t>나래초</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>미술교실</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1486,25 +1848,35 @@
           <t>나래초</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>미술교실</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n">
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1514,25 +1886,35 @@
           <t>나래초</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>로봇과학</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="4" t="n">
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1542,25 +1924,35 @@
           <t>나래초</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>로봇과학</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="4" t="n">
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1570,25 +1962,35 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>과학실험</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="4" t="n">
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="4" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1598,25 +2000,35 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>과학실험</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1626,25 +2038,35 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>시사토론</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n">
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>42</v>
       </c>
     </row>
@@ -1654,25 +2076,35 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>시사토론</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="n">
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="H43" s="4" t="n">
         <v>71</v>
       </c>
     </row>
@@ -1682,25 +2114,35 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>영문법</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="n">
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <v>47</v>
       </c>
     </row>
@@ -1710,25 +2152,35 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>영문법</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="n">
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>44</v>
       </c>
     </row>
@@ -1738,25 +2190,35 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>수학사고력</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="4" t="n">
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="4" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1766,25 +2228,35 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>수학사고력</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="n">
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>40</v>
       </c>
     </row>
@@ -1794,25 +2266,35 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>농구교실</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="4" t="n">
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1822,25 +2304,35 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>농구교실</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="n">
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="H49" s="4" t="n">
         <v>40</v>
       </c>
     </row>
@@ -1850,25 +2342,35 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>배드민턴</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="4" t="n">
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="4" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1878,25 +2380,35 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>배드민턴</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="n">
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="H51" s="4" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1906,25 +2418,35 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>축구교실</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="n">
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="H52" s="4" t="n">
         <v>32</v>
       </c>
     </row>
@@ -1934,23 +2456,33 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>축구교실</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="n"/>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1958,25 +2490,35 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="4" t="n">
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1986,25 +2528,35 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="4" t="n">
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="4" t="n">
         <v>16</v>
       </c>
     </row>
@@ -2014,25 +2566,35 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>피아노</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" s="4" t="n">
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="4" t="n">
         <v>21</v>
       </c>
     </row>
@@ -2042,25 +2604,35 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>피아노</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="n">
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="H57" s="4" t="n">
         <v>34</v>
       </c>
     </row>
@@ -2070,25 +2642,35 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>드론교실</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" s="4" t="n">
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2098,25 +2680,35 @@
           <t>다온초</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>드론교실</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" s="4" t="n">
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -2126,25 +2718,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>글쓰기교실</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="n">
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F60" s="4" t="n">
+      <c r="H60" s="4" t="n">
         <v>54</v>
       </c>
     </row>
@@ -2154,23 +2756,33 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>글쓰기교실</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="n"/>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2178,25 +2790,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>한국사</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="n">
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F62" s="4" t="n">
+      <c r="H62" s="4" t="n">
         <v>27</v>
       </c>
     </row>
@@ -2206,25 +2828,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>한국사</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="n">
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F63" s="4" t="n">
+      <c r="H63" s="4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2234,25 +2866,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>사회탐구</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" s="4" t="n">
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -2262,25 +2904,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>사회탐구</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="4" t="n">
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" s="4" t="n">
         <v>22</v>
       </c>
     </row>
@@ -2290,25 +2942,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>수학사고력</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="n">
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F66" s="4" t="n">
+      <c r="H66" s="4" t="n">
         <v>24</v>
       </c>
     </row>
@@ -2318,25 +2980,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>수학사고력</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="n">
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F67" s="4" t="n">
+      <c r="H67" s="4" t="n">
         <v>38</v>
       </c>
     </row>
@@ -2346,25 +3018,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>시사토론</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="n">
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F68" s="4" t="n">
+      <c r="H68" s="4" t="n">
         <v>29</v>
       </c>
     </row>
@@ -2374,25 +3056,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>시사토론</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="n">
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F69" s="4" t="n">
+      <c r="H69" s="4" t="n">
         <v>37</v>
       </c>
     </row>
@@ -2402,25 +3094,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>미술교실</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="4" t="n">
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="4" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2430,25 +3132,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>미술교실</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" s="4" t="n">
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -2458,25 +3170,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>합창단</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" s="4" t="n">
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" s="4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -2486,25 +3208,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>합창단</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" s="4" t="n">
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="4" t="n">
         <v>14</v>
       </c>
     </row>
@@ -2514,25 +3246,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>방송댄스</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" s="4" t="n">
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="4" t="n">
         <v>21</v>
       </c>
     </row>
@@ -2542,25 +3284,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>방송댄스</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" s="4" t="n">
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" s="4" t="n">
         <v>16</v>
       </c>
     </row>
@@ -2570,25 +3322,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>바이올린</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" s="4" t="n">
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -2598,25 +3360,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>바이올린</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" s="4" t="n">
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -2626,25 +3398,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="4" t="n">
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -2654,25 +3436,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="4" t="n">
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -2682,25 +3474,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>메이커교실</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" s="4" t="n">
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="4" t="n">
         <v>18</v>
       </c>
     </row>
@@ -2710,25 +3512,35 @@
           <t>라온초</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>메이커교실</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" s="4" t="n">
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="4" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2738,25 +3550,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>과학실험</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F82" s="4" t="n">
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2766,25 +3588,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>과학실험</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" s="4" t="n">
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="4" t="n">
         <v>21</v>
       </c>
     </row>
@@ -2794,25 +3626,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>한국사</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F84" s="4" t="n">
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2822,23 +3664,33 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>한국사</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="n"/>
-      <c r="F85" s="5" t="n"/>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="n"/>
+      <c r="H85" s="5" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2846,25 +3698,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>독서논술</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F86" s="4" t="n">
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -2874,25 +3736,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>독서논술</t>
         </is>
       </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F87" s="4" t="n">
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2902,25 +3774,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>영어회화</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" s="4" t="n">
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2930,25 +3812,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>영어회화</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="n">
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F89" s="4" t="n">
+      <c r="H89" s="4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2958,25 +3850,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>사회탐구</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" s="4" t="n">
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="4" t="n">
         <v>16</v>
       </c>
     </row>
@@ -2986,25 +3888,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>사회탐구</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F91" s="4" t="n">
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="4" t="n">
         <v>21</v>
       </c>
     </row>
@@ -3014,25 +3926,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>합창단</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="n">
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F92" s="4" t="n">
+      <c r="H92" s="4" t="n">
         <v>32</v>
       </c>
     </row>
@@ -3042,25 +3964,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>합창단</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="n">
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F93" s="4" t="n">
+      <c r="H93" s="4" t="n">
         <v>27</v>
       </c>
     </row>
@@ -3070,25 +4002,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>농구교실</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="n">
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F94" s="4" t="n">
+      <c r="H94" s="4" t="n">
         <v>45</v>
       </c>
     </row>
@@ -3098,25 +4040,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>농구교실</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="n">
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F95" s="4" t="n">
+      <c r="H95" s="4" t="n">
         <v>61</v>
       </c>
     </row>
@@ -3126,25 +4078,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>배드민턴</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="n">
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="H96" s="4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -3154,25 +4116,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>배드민턴</t>
         </is>
       </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="n">
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="H97" s="4" t="n">
         <v>38</v>
       </c>
     </row>
@@ -3182,25 +4154,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>미술교실</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="n">
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F98" s="4" t="n">
+      <c r="H98" s="4" t="n">
         <v>51</v>
       </c>
     </row>
@@ -3210,25 +4192,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>미술교실</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="n">
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F99" s="4" t="n">
+      <c r="H99" s="4" t="n">
         <v>50</v>
       </c>
     </row>
@@ -3238,25 +4230,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>AI기초</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F100" s="4" t="n">
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" s="4" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3266,25 +4268,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>AI기초</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F101" s="4" t="n">
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -3294,25 +4306,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>3D프린팅</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="n">
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F102" s="4" t="n">
+      <c r="H102" s="4" t="n">
         <v>37</v>
       </c>
     </row>
@@ -3322,25 +4344,35 @@
           <t>마루초</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>3D프린팅</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="n">
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F103" s="4" t="n">
+      <c r="H103" s="4" t="n">
         <v>26</v>
       </c>
     </row>
@@ -3350,25 +4382,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>시사토론</t>
         </is>
       </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F104" s="4" t="n">
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="4" t="n">
         <v>16</v>
       </c>
     </row>
@@ -3378,25 +4420,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>시사토론</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F105" s="4" t="n">
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" s="4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -3406,25 +4458,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>글쓰기교실</t>
         </is>
       </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F106" s="4" t="n">
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -3434,25 +4496,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>글쓰기교실</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F107" s="4" t="n">
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" s="4" t="n">
         <v>14</v>
       </c>
     </row>
@@ -3462,25 +4534,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>영어회화</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E108" s="4" t="n">
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F108" s="4" t="n">
+      <c r="H108" s="4" t="n">
         <v>41</v>
       </c>
     </row>
@@ -3490,25 +4572,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>영어회화</t>
         </is>
       </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="n">
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F109" s="4" t="n">
+      <c r="H109" s="4" t="n">
         <v>41</v>
       </c>
     </row>
@@ -3518,25 +4610,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>과학실험</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="n">
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F110" s="4" t="n">
+      <c r="H110" s="4" t="n">
         <v>28</v>
       </c>
     </row>
@@ -3546,25 +4648,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>과학실험</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F111" s="4" t="n">
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -3574,25 +4686,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>사회탐구</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E112" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F112" s="4" t="n">
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" s="4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3602,25 +4724,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>사회탐구</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F113" s="4" t="n">
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" s="4" t="n">
         <v>22</v>
       </c>
     </row>
@@ -3630,25 +4762,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>바이올린</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E114" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F114" s="4" t="n">
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" s="4" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3658,25 +4800,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>바이올린</t>
         </is>
       </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F115" s="4" t="n">
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" s="4" t="n">
         <v>18</v>
       </c>
     </row>
@@ -3686,25 +4838,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>방송댄스</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E116" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F116" s="4" t="n">
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -3714,25 +4876,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>방송댄스</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F117" s="4" t="n">
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" s="4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -3742,25 +4914,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>난타</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E118" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F118" s="4" t="n">
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" s="4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3770,25 +4952,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>난타</t>
         </is>
       </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E119" s="4" t="n">
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F119" s="4" t="n">
+      <c r="H119" s="4" t="n">
         <v>43</v>
       </c>
     </row>
@@ -3798,25 +4990,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E120" s="4" t="n">
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F120" s="4" t="n">
+      <c r="H120" s="4" t="n">
         <v>35</v>
       </c>
     </row>
@@ -3826,25 +5028,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="n">
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F121" s="4" t="n">
+      <c r="H121" s="4" t="n">
         <v>28</v>
       </c>
     </row>
@@ -3854,25 +5066,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>축구교실</t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E122" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F122" s="4" t="n">
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" s="4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3882,25 +5104,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>축구교실</t>
         </is>
       </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E123" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F123" s="4" t="n">
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" s="4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3910,25 +5142,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>드론교실</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E124" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F124" s="4" t="n">
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" s="4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -3938,25 +5180,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>드론교실</t>
         </is>
       </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E125" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F125" s="4" t="n">
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -3966,25 +5218,35 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>코딩</t>
         </is>
       </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="n">
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F126" s="4" t="n">
+      <c r="H126" s="4" t="n">
         <v>60</v>
       </c>
     </row>
@@ -3994,23 +5256,33 @@
           <t>바롬초</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>코딩</t>
         </is>
       </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E127" s="5" t="n"/>
-      <c r="F127" s="5" t="n"/>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="n"/>
+      <c r="H127" s="5" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -4018,25 +5290,35 @@
           <t>사랑초</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>수학사고력</t>
         </is>
       </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E128" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F128" s="4" t="n">
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" s="4" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4046,25 +5328,35 @@
           <t>사랑초</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>수학사고력</t>
         </is>
       </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E129" s="4" t="n">
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F129" s="4" t="n">
+      <c r="H129" s="4" t="n">
         <v>32</v>
       </c>
     </row>
@@ -4074,25 +5366,35 @@
           <t>사랑초</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>글쓰기교실</t>
         </is>
       </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F130" s="4" t="n">
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" s="4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4102,25 +5404,35 @@
           <t>사랑초</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>글쓰기교실</t>
         </is>
       </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F131" s="4" t="n">
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" s="4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -4130,25 +5442,35 @@
           <t>사랑초</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>시사토론</t>
         </is>
       </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="n">
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F132" s="4" t="n">
+      <c r="H132" s="4" t="n">
         <v>48</v>
       </c>
     </row>
@@ -4158,25 +5480,35 @@
           <t>사랑초</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>시사토론</t>
         </is>
       </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E133" s="4" t="n">
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F133" s="4" t="n">
+      <c r="H133" s="4" t="n">
         <v>62</v>
       </c>
     </row>
@@ -4186,25 +5518,35 @@
           <t>사랑초</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>영어회화</t>
         </is>
       </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E134" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F134" s="4" t="n">
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" s="4" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4214,23 +5556,33 @@
           <t>사랑초</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>영어회화</t>
         </is>
       </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="n"/>
-      <c r="F135" s="5" t="n"/>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="n"/>
+      <c r="H135" s="5" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -4238,25 +5590,35 @@
           <t>사랑초</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>방송댄스</t>
         </is>
       </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E136" s="4" t="n">
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F136" s="4" t="n">
+      <c r="H136" s="4" t="n">
         <v>32</v>
       </c>
     </row>
@@ -4266,25 +5628,35 @@
           <t>사랑초</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>방송댄스</t>
         </is>
       </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E137" s="4" t="n">
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F137" s="4" t="n">
+      <c r="H137" s="4" t="n">
         <v>34</v>
       </c>
     </row>
@@ -4294,25 +5666,35 @@
           <t>사랑초</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>농구교실</t>
         </is>
       </c>
-      <c r="D138" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E138" s="4" t="n">
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F138" s="4" t="n">
+      <c r="H138" s="4" t="n">
         <v>34</v>
       </c>
     </row>
@@ -4322,25 +5704,35 @@
           <t>사랑초</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>농구교실</t>
         </is>
       </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E139" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F139" s="4" t="n">
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" s="4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -4350,25 +5742,35 @@
           <t>사랑초</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>피아노</t>
         </is>
       </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E140" s="4" t="n">
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F140" s="4" t="n">
+      <c r="H140" s="4" t="n">
         <v>43</v>
       </c>
     </row>
@@ -4378,25 +5780,35 @@
           <t>사랑초</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>피아노</t>
         </is>
       </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E141" s="4" t="n">
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F141" s="4" t="n">
+      <c r="H141" s="4" t="n">
         <v>49</v>
       </c>
     </row>
@@ -4406,25 +5818,35 @@
           <t>사랑초</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>축구교실</t>
         </is>
       </c>
-      <c r="D142" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E142" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F142" s="4" t="n">
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" s="4" t="n">
         <v>16</v>
       </c>
     </row>
@@ -4434,25 +5856,35 @@
           <t>사랑초</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>축구교실</t>
         </is>
       </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E143" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F143" s="4" t="n">
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -4462,25 +5894,35 @@
           <t>사랑초</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>코딩</t>
         </is>
       </c>
-      <c r="D144" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E144" s="4" t="n">
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F144" s="4" t="n">
+      <c r="H144" s="4" t="n">
         <v>27</v>
       </c>
     </row>
@@ -4490,25 +5932,35 @@
           <t>사랑초</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>코딩</t>
         </is>
       </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E145" s="4" t="n">
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F145" s="4" t="n">
+      <c r="H145" s="4" t="n">
         <v>36</v>
       </c>
     </row>
@@ -4518,25 +5970,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>과학실험</t>
         </is>
       </c>
-      <c r="D146" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E146" s="4" t="n">
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F146" s="4" t="n">
+      <c r="H146" s="4" t="n">
         <v>48</v>
       </c>
     </row>
@@ -4546,25 +6008,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>과학실험</t>
         </is>
       </c>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E147" s="4" t="n">
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F147" s="4" t="n">
+      <c r="H147" s="4" t="n">
         <v>37</v>
       </c>
     </row>
@@ -4574,25 +6046,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>독서논술</t>
         </is>
       </c>
-      <c r="D148" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E148" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F148" s="4" t="n">
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" s="4" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4602,25 +6084,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>독서논술</t>
         </is>
       </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E149" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F149" s="4" t="n">
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" s="4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4630,25 +6122,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>사회탐구</t>
         </is>
       </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E150" s="4" t="n">
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F150" s="4" t="n">
+      <c r="H150" s="4" t="n">
         <v>47</v>
       </c>
     </row>
@@ -4658,25 +6160,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>사회탐구</t>
         </is>
       </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E151" s="4" t="n">
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G151" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F151" s="4" t="n">
+      <c r="H151" s="4" t="n">
         <v>52</v>
       </c>
     </row>
@@ -4686,25 +6198,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>수학사고력</t>
         </is>
       </c>
-      <c r="D152" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E152" s="4" t="n">
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F152" s="4" t="n">
+      <c r="H152" s="4" t="n">
         <v>32</v>
       </c>
     </row>
@@ -4714,25 +6236,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>수학사고력</t>
         </is>
       </c>
-      <c r="D153" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E153" s="4" t="n">
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F153" s="4" t="n">
+      <c r="H153" s="4" t="n">
         <v>29</v>
       </c>
     </row>
@@ -4742,25 +6274,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>한자교실</t>
         </is>
       </c>
-      <c r="D154" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E154" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F154" s="4" t="n">
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" s="4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -4770,25 +6312,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>한자교실</t>
         </is>
       </c>
-      <c r="D155" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E155" s="4" t="n">
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G155" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F155" s="4" t="n">
+      <c r="H155" s="4" t="n">
         <v>38</v>
       </c>
     </row>
@@ -4798,25 +6350,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>배드민턴</t>
         </is>
       </c>
-      <c r="D156" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E156" s="4" t="n">
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F156" s="4" t="n">
+      <c r="H156" s="4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -4826,25 +6388,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>배드민턴</t>
         </is>
       </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E157" s="4" t="n">
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G157" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F157" s="4" t="n">
+      <c r="H157" s="4" t="n">
         <v>51</v>
       </c>
     </row>
@@ -4854,25 +6426,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>바이올린</t>
         </is>
       </c>
-      <c r="D158" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E158" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F158" s="4" t="n">
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" s="4" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4882,25 +6464,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>바이올린</t>
         </is>
       </c>
-      <c r="D159" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E159" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F159" s="4" t="n">
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G159" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" s="4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4910,25 +6502,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>난타</t>
         </is>
       </c>
-      <c r="D160" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E160" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F160" s="4" t="n">
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" s="4" t="n">
         <v>18</v>
       </c>
     </row>
@@ -4938,25 +6540,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>난타</t>
         </is>
       </c>
-      <c r="D161" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E161" s="4" t="n">
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F161" s="4" t="n">
+      <c r="H161" s="4" t="n">
         <v>36</v>
       </c>
     </row>
@@ -4966,25 +6578,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>미술교실</t>
         </is>
       </c>
-      <c r="D162" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E162" s="4" t="n">
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F162" s="4" t="n">
+      <c r="H162" s="4" t="n">
         <v>48</v>
       </c>
     </row>
@@ -4994,25 +6616,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>미술교실</t>
         </is>
       </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E163" s="4" t="n">
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F163" s="4" t="n">
+      <c r="H163" s="4" t="n">
         <v>67</v>
       </c>
     </row>
@@ -5022,25 +6654,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>3D프린팅</t>
         </is>
       </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F164" s="4" t="n">
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G164" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H164" s="4" t="n">
         <v>14</v>
       </c>
     </row>
@@ -5050,25 +6692,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>3D프린팅</t>
         </is>
       </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E165" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F165" s="4" t="n">
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5078,25 +6730,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>AI기초</t>
         </is>
       </c>
-      <c r="D166" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="n">
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F166" s="4" t="n">
+      <c r="H166" s="4" t="n">
         <v>28</v>
       </c>
     </row>
@@ -5106,25 +6768,35 @@
           <t>아람초</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>AI기초</t>
         </is>
       </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="n">
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F167" s="4" t="n">
+      <c r="H167" s="4" t="n">
         <v>31</v>
       </c>
     </row>
@@ -5134,25 +6806,35 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>한국사</t>
         </is>
       </c>
-      <c r="D168" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E168" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F168" s="4" t="n">
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H168" s="4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5162,25 +6844,35 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>한국사</t>
         </is>
       </c>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E169" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F169" s="4" t="n">
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" s="4" t="n">
         <v>18</v>
       </c>
     </row>
@@ -5190,25 +6882,35 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>수학사고력</t>
         </is>
       </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F170" s="4" t="n">
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G170" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" s="4" t="n">
         <v>21</v>
       </c>
     </row>
@@ -5218,25 +6920,35 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>수학사고력</t>
         </is>
       </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E171" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F171" s="4" t="n">
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G171" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" s="4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5246,25 +6958,35 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>독서논술</t>
         </is>
       </c>
-      <c r="D172" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="n">
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G172" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F172" s="4" t="n">
+      <c r="H172" s="4" t="n">
         <v>34</v>
       </c>
     </row>
@@ -5274,25 +6996,35 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>독서논술</t>
         </is>
       </c>
-      <c r="D173" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E173" s="4" t="n">
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G173" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F173" s="4" t="n">
+      <c r="H173" s="4" t="n">
         <v>53</v>
       </c>
     </row>
@@ -5302,25 +7034,35 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>사회탐구</t>
         </is>
       </c>
-      <c r="D174" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E174" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F174" s="4" t="n">
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G174" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" s="4" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5330,25 +7072,35 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>사회탐구</t>
         </is>
       </c>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E175" s="4" t="n">
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F175" s="4" t="n">
+      <c r="H175" s="4" t="n">
         <v>35</v>
       </c>
     </row>
@@ -5358,25 +7110,35 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>바이올린</t>
         </is>
       </c>
-      <c r="D176" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E176" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F176" s="4" t="n">
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" s="4" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5386,25 +7148,35 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>바이올린</t>
         </is>
       </c>
-      <c r="D177" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E177" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F177" s="4" t="n">
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" s="4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5414,25 +7186,35 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="D178" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E178" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F178" s="4" t="n">
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G178" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5442,25 +7224,35 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="D179" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E179" s="4" t="n">
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G179" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F179" s="4" t="n">
+      <c r="H179" s="4" t="n">
         <v>26</v>
       </c>
     </row>
@@ -5470,25 +7262,35 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>방송댄스</t>
         </is>
       </c>
-      <c r="D180" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E180" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F180" s="4" t="n">
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G180" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -5498,25 +7300,35 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>방송댄스</t>
         </is>
       </c>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E181" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F181" s="4" t="n">
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" s="4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5526,25 +7338,35 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>피아노</t>
         </is>
       </c>
-      <c r="D182" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E182" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F182" s="4" t="n">
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H182" s="4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5554,25 +7376,35 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>피아노</t>
         </is>
       </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E183" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F183" s="4" t="n">
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G183" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H183" s="4" t="n">
         <v>14</v>
       </c>
     </row>
@@ -5582,25 +7414,35 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>난타</t>
         </is>
       </c>
-      <c r="D184" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E184" s="4" t="n">
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G184" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F184" s="4" t="n">
+      <c r="H184" s="4" t="n">
         <v>33</v>
       </c>
     </row>
@@ -5610,23 +7452,33 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>난타</t>
         </is>
       </c>
-      <c r="D185" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E185" s="5" t="n"/>
-      <c r="F185" s="5" t="n"/>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="n"/>
+      <c r="H185" s="5" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -5634,25 +7486,35 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>AI기초</t>
         </is>
       </c>
-      <c r="D186" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E186" s="4" t="n">
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G186" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F186" s="4" t="n">
+      <c r="H186" s="4" t="n">
         <v>53</v>
       </c>
     </row>
@@ -5662,25 +7524,35 @@
           <t>한솔초</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>AI기초</t>
         </is>
       </c>
-      <c r="D187" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E187" s="4" t="n">
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G187" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F187" s="4" t="n">
+      <c r="H187" s="4" t="n">
         <v>61</v>
       </c>
     </row>
@@ -5690,25 +7562,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>한자교실</t>
         </is>
       </c>
-      <c r="D188" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E188" s="4" t="n">
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G188" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F188" s="4" t="n">
+      <c r="H188" s="4" t="n">
         <v>25</v>
       </c>
     </row>
@@ -5718,25 +7600,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>한자교실</t>
         </is>
       </c>
-      <c r="D189" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E189" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F189" s="4" t="n">
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G189" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H189" s="4" t="n">
         <v>18</v>
       </c>
     </row>
@@ -5746,25 +7638,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>과학실험</t>
         </is>
       </c>
-      <c r="D190" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E190" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F190" s="4" t="n">
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G190" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H190" s="4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5774,25 +7676,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>과학실험</t>
         </is>
       </c>
-      <c r="D191" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E191" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F191" s="4" t="n">
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G191" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H191" s="4" t="n">
         <v>14</v>
       </c>
     </row>
@@ -5802,25 +7714,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>사회탐구</t>
         </is>
       </c>
-      <c r="D192" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E192" s="4" t="n">
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F192" s="4" t="n">
+      <c r="H192" s="4" t="n">
         <v>28</v>
       </c>
     </row>
@@ -5830,25 +7752,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>사회탐구</t>
         </is>
       </c>
-      <c r="D193" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E193" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F193" s="4" t="n">
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G193" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H193" s="4" t="n">
         <v>18</v>
       </c>
     </row>
@@ -5858,25 +7790,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>독서논술</t>
         </is>
       </c>
-      <c r="D194" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E194" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F194" s="4" t="n">
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G194" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" s="4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5886,25 +7828,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>교과</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>독서논술</t>
         </is>
       </c>
-      <c r="D195" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E195" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F195" s="4" t="n">
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G195" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" s="4" t="n">
         <v>22</v>
       </c>
     </row>
@@ -5914,25 +7866,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>배드민턴</t>
         </is>
       </c>
-      <c r="D196" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E196" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F196" s="4" t="n">
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G196" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H196" s="4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5942,25 +7904,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>배드민턴</t>
         </is>
       </c>
-      <c r="D197" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E197" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F197" s="4" t="n">
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G197" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" s="4" t="n">
         <v>18</v>
       </c>
     </row>
@@ -5970,25 +7942,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>농구교실</t>
         </is>
       </c>
-      <c r="D198" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E198" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F198" s="4" t="n">
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G198" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" s="4" t="n">
         <v>18</v>
       </c>
     </row>
@@ -5998,25 +7980,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>농구교실</t>
         </is>
       </c>
-      <c r="D199" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E199" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F199" s="4" t="n">
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G199" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H199" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -6026,25 +8018,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>축구교실</t>
         </is>
       </c>
-      <c r="D200" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E200" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F200" s="4" t="n">
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G200" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H200" s="4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -6054,25 +8056,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>축구교실</t>
         </is>
       </c>
-      <c r="D201" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E201" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F201" s="4" t="n">
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G201" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H201" s="4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -6082,25 +8094,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>피아노</t>
         </is>
       </c>
-      <c r="D202" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E202" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F202" s="4" t="n">
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G202" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" s="4" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6110,25 +8132,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>예체능</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>피아노</t>
         </is>
       </c>
-      <c r="D203" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E203" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F203" s="4" t="n">
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G203" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H203" s="4" t="n">
         <v>16</v>
       </c>
     </row>
@@ -6138,25 +8170,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>메이커교실</t>
         </is>
       </c>
-      <c r="D204" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E204" s="4" t="n">
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G204" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F204" s="4" t="n">
+      <c r="H204" s="4" t="n">
         <v>45</v>
       </c>
     </row>
@@ -6166,25 +8208,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C205" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>메이커교실</t>
         </is>
       </c>
-      <c r="D205" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E205" s="4" t="n">
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G205" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F205" s="4" t="n">
+      <c r="H205" s="4" t="n">
         <v>45</v>
       </c>
     </row>
@@ -6194,25 +8246,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C206" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>3D프린팅</t>
         </is>
       </c>
-      <c r="D206" s="3" t="inlineStr">
-        <is>
-          <t>1학기</t>
-        </is>
-      </c>
-      <c r="E206" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F206" s="4" t="n">
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>1학기</t>
+        </is>
+      </c>
+      <c r="G206" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H206" s="4" t="n">
         <v>19</v>
       </c>
     </row>
@@ -6222,25 +8284,35 @@
           <t>해솔초</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>정보</t>
         </is>
       </c>
-      <c r="C207" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>3D프린팅</t>
         </is>
       </c>
-      <c r="D207" s="3" t="inlineStr">
-        <is>
-          <t>2학기</t>
-        </is>
-      </c>
-      <c r="E207" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F207" s="4" t="n">
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>2학기</t>
+        </is>
+      </c>
+      <c r="G207" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H207" s="4" t="n">
         <v>21</v>
       </c>
     </row>
@@ -6255,7 +8327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6501,6 +8573,193 @@
         <v>2751</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>지역</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>1학기 강좌수</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>1학기 수강인원</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>2학기 강좌수</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>2학기 수강인원</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>동부</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>898</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>서부</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>824</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>남부</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>759</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>158</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>2481</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>164</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>2751</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>설립</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>1학기 강좌수</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>1학기 수강인원</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>2학기 강좌수</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>2학기 수강인원</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>공립</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>1418</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>사립</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>1063</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>158</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>2481</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>164</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>2751</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6512,7 +8771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="105" customWidth="1" min="1" max="1"/>
@@ -6555,7 +8814,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>1) 취합 : 원본 폴더의 3개 학교 파일을 VBA로 한 번에 쌓는다 (A열=파일명, B열=시트명).</t>
+          <t>1) 취합 : 원본 폴더의 학교 파일들을 VBA로 한 번에 쌓는다 (A열=파일명, B열=시트명).</t>
         </is>
       </c>
     </row>
@@ -6597,17 +8856,38 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>7) 분석 : 피벗테이블로 학교별/학기별 강좌수 합계, 수강인원 합계를 만든다.</t>
+          <t>7) 학교·지역·설립 열 : 파일명으로 학교 열을 만들고, '학교속성표.xlsx'를 VLOOKUP/병합해 지역·설립을 붙인다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr"/>
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (심화 시연) 원본 3행의 '지역/설립' 텍스트에서 직접 추출하는 방법도 있음 - 함수/파워쿼리/AI 추가기능 활용.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>이 통합문서의 '데이터형' 시트가 2~6단계의 정답, '피벗요약' 시트가 7단계의 정답이다.</t>
+          <t>8) 분석 : 피벗테이블로 학교별/지역별/공사립별 x 학기별 강좌수·수강인원 합계를 만든다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>핵심: 데이터가 많아도 데이터형으로 정리해 두면 파워쿼리가 자동으로 처리하고, 집계 기준(지역·공사립 등)은 피벗에서 즉시 바꿀 수 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>이 통합문서의 '데이터형' 시트가 2~6단계의 정답, '피벗요약' 시트가 8단계의 정답이다.</t>
         </is>
       </c>
     </row>
